--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,6 +1129,125 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128553744</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97654</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pumpkälleskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>372517</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6390146</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Även sporblad.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Berglund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Berglund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97654</v>
+        <v>97660</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97660</v>
+        <v>97666</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97666</v>
+        <v>97668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97669</v>
+        <v>97696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97696</v>
+        <v>97702</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97702</v>
+        <v>97709</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97709</v>
+        <v>97713</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97713</v>
+        <v>97720</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97723</v>
+        <v>97728</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -1134,7 +1134,7 @@
         <v>128553744</v>
       </c>
       <c r="B6" t="n">
-        <v>97728</v>
+        <v>97736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112333788</v>
       </c>
       <c r="B2" t="n">
-        <v>95067</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,12 +785,7 @@
         <v>112487194</v>
       </c>
       <c r="B3" t="n">
-        <v>95136</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +821,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>372532</v>
+        <v>372533</v>
       </c>
       <c r="R3" t="n">
         <v>6390327</v>
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112487201</v>
+        <v>112487269</v>
       </c>
       <c r="B4" t="n">
-        <v>93346</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97733</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,25 +900,33 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(L.) Gray</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -943,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>372532</v>
+        <v>372636</v>
       </c>
       <c r="R4" t="n">
-        <v>6390327</v>
+        <v>6390362</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -983,7 +976,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Större fläck.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,15 +1004,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112487269</v>
+        <v>112487201</v>
       </c>
       <c r="B5" t="n">
-        <v>95136</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,33 +1015,25 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2569</v>
+        <v>2810</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -1063,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>372636</v>
+        <v>372533</v>
       </c>
       <c r="R5" t="n">
-        <v>6390362</v>
+        <v>6390327</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1103,7 +1083,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Större fläck.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,10 +1111,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128553744</v>
+        <v>112333750</v>
       </c>
       <c r="B6" t="n">
-        <v>97736</v>
+        <v>57947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1142,53 +1122,49 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220686</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kambräken</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Blechnum spicant</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Roth</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pumpkälleskogen, Vg</t>
+          <t>Ryttarenområdet, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>372517</v>
+        <v>372484</v>
       </c>
       <c r="R6" t="n">
-        <v>6390146</v>
+        <v>6390317</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,17 +1188,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Även sporblad.</t>
+          <t>Hörd, flygande.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,22 +1217,365 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>96623805</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>200m sydväst Skansen Viskafors, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>372585</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6390319</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2021-10-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lars Aspholmer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lars Aspholmer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>112487221</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Skanen-området, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>372490</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6390327</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Minst 2 ex.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lars Gerre</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128553744</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98194</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220686</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kambräken</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Blechnum spicant</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Roth</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Pumpkälleskogen, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>372517</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6390146</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Borås</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kinnarumma</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Även sporblad.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Lars Berglund</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Lars Berglund</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3764-2024 artfynd.xlsx
+++ b/artfynd/A 3764-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112333788</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112487194</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112487269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112487201</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112333750</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96623805</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112487221</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1576,8 +1616,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128553744</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>